--- a/Assets/Plugins/ES/3_Examples/3_Data/Example_SOTableRule/03_Tables/xlsx/ExampleNativeSoListTableSource_Example.xlsx
+++ b/Assets/Plugins/ES/3_Examples/3_Data/Example_SOTableRule/03_Tables/xlsx/ExampleNativeSoListTableSource_Example.xlsx
@@ -419,116 +419,116 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>reward_holder_001</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>第1组奖励</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>reward_005</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>体力补给05</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>TestOnly</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>串行List行，归属 reward_holder_001 #05</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>##assert</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>required;unique</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>required;unique</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>reward_holder_001</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>第1组奖励</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>reward_006</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>钥匙碎片06</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>串行List行，归属 reward_holder_001 #06</t>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>##rowDirective | 空=正常导入；skip/ignore/disabled=跳过；comment:=备注；required=整行和Key必填；patch=只写非空；replace=强制覆盖；owner=只写SO本体；delete=删除；debug=打印本行追踪；debug:patch/debug:delete=按真实指令执行并打印</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
@@ -555,37 +555,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>reward_007</t>
+          <t>reward_005</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>活动代币07</t>
+          <t>体力补给05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>TestOnly</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_001 #07</t>
+          <t>串行List行，归属 reward_holder_001 #05</t>
         </is>
       </c>
     </row>
@@ -612,37 +612,37 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>reward_008</t>
+          <t>reward_006</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>装备图纸08</t>
+          <t>钥匙碎片06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_001 #08</t>
+          <t>串行List行，归属 reward_holder_001 #06</t>
         </is>
       </c>
     </row>
@@ -669,37 +669,37 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>reward_009</t>
+          <t>reward_007</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>技能书09</t>
+          <t>活动代币07</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tradable, Stackable</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_001 #09</t>
+          <t>串行List行，归属 reward_holder_001 #07</t>
         </is>
       </c>
     </row>
@@ -726,37 +726,37 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>reward_010</t>
+          <t>reward_008</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>宝石礼包10</t>
+          <t>装备图纸08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TestOnly</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_001 #10</t>
+          <t>串行List行，归属 reward_holder_001 #08</t>
         </is>
       </c>
     </row>
@@ -783,37 +783,37 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>reward_001</t>
+          <t>reward_009</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>通关金币2323</t>
+          <t>技能书09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>Tradable, Stackable</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>嵌套字段测试</t>
+          <t>串行List行，归属 reward_holder_001 #09</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>reward_holder_002</t>
+          <t>reward_holder_001</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>第2组奖励</t>
+          <t>第1组奖励</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -840,12 +840,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>reward_001</t>
+          <t>reward_010</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>通关金币</t>
+          <t>宝石礼包10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>TestOnly</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>嵌套字段测试</t>
+          <t>串行List行，归属 reward_holder_001 #10</t>
         </is>
       </c>
     </row>
@@ -882,12 +882,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>reward_holder_002</t>
+          <t>reward_holder_001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>第2组奖励</t>
+          <t>第1组奖励</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -897,27 +897,27 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>reward_002</t>
+          <t>reward_001</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>稀有宝箱</t>
+          <t>通关金币2323</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>999</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -954,37 +954,37 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>reward_011</t>
+          <t>reward_001</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>通关金币11</t>
+          <t>通关金币</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #11</t>
+          <t>嵌套字段测试</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>reward_012</t>
+          <t>reward_002</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>稀有宝箱12999</t>
+          <t>稀有宝箱</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #12</t>
+          <t>嵌套字段测试</t>
         </is>
       </c>
     </row>
@@ -1068,37 +1068,37 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>reward_013</t>
+          <t>reward_011</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>经验药水13</t>
+          <t>通关金币11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #13</t>
+          <t>串行List行，归属 reward_holder_002 #11</t>
         </is>
       </c>
     </row>
@@ -1125,37 +1125,37 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>reward_014</t>
+          <t>reward_012</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>强化石14</t>
+          <t>稀有宝箱12999</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tradable, Stackable</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #14</t>
+          <t>串行List行，归属 reward_holder_002 #12</t>
         </is>
       </c>
     </row>
@@ -1182,37 +1182,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>reward_015</t>
+          <t>reward_013</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>体力补给15</t>
+          <t>经验药水13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TestOnly</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #15</t>
+          <t>串行List行，归属 reward_holder_002 #13</t>
         </is>
       </c>
     </row>
@@ -1239,37 +1239,37 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>reward_016</t>
+          <t>reward_014</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>钥匙碎片16</t>
+          <t>强化石14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Tradable, Stackable</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #16</t>
+          <t>串行List行，归属 reward_holder_002 #14</t>
         </is>
       </c>
     </row>
@@ -1296,37 +1296,37 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>reward_017</t>
+          <t>reward_015</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>活动代币17</t>
+          <t>体力补给15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>TestOnly</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #17</t>
+          <t>串行List行，归属 reward_holder_002 #15</t>
         </is>
       </c>
     </row>
@@ -1353,37 +1353,37 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>reward_018</t>
+          <t>reward_016</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>装备图纸18</t>
+          <t>钥匙碎片16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>130</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #18</t>
+          <t>串行List行，归属 reward_holder_002 #16</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1410,37 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>reward_019</t>
+          <t>reward_017</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>技能书19</t>
+          <t>活动代币17</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Tradable, Stackable</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #19</t>
+          <t>串行List行，归属 reward_holder_002 #17</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>reward_020</t>
+          <t>reward_018</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>宝石礼包20</t>
+          <t>装备图纸18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1482,22 +1482,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>TestOnly</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_002 #20</t>
+          <t>串行List行，归属 reward_holder_002 #18</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>reward_holder_003</t>
+          <t>reward_holder_002</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>第3组奖励</t>
+          <t>第2组奖励</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>reward_001</t>
+          <t>reward_019</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>通关金币</t>
+          <t>技能书19</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>145</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>Tradable, Stackable</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>嵌套字段测试</t>
+          <t>串行List行，归属 reward_holder_002 #19</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>reward_holder_003</t>
+          <t>reward_holder_002</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>第3组奖励</t>
+          <t>第2组奖励</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>reward_002</t>
+          <t>reward_020</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>稀有宝箱</t>
+          <t>宝石礼包20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>TestOnly</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>嵌套字段测试</t>
+          <t>串行List行，归属 reward_holder_002 #20</t>
         </is>
       </c>
     </row>
@@ -1638,37 +1638,37 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>reward_021</t>
+          <t>reward_001</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>通关金币21</t>
+          <t>通关金币</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #21</t>
+          <t>嵌套字段测试</t>
         </is>
       </c>
     </row>
@@ -1695,37 +1695,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>reward_022</t>
+          <t>reward_002</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>稀有宝箱22</t>
+          <t>稀有宝箱</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #22</t>
+          <t>嵌套字段测试</t>
         </is>
       </c>
     </row>
@@ -1752,37 +1752,37 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>reward_023</t>
+          <t>reward_021</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>经验药水23</t>
+          <t>通关金币21</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #23</t>
+          <t>串行List行，归属 reward_holder_003 #21</t>
         </is>
       </c>
     </row>
@@ -1809,37 +1809,37 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>reward_024</t>
+          <t>reward_022</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>强化石24</t>
+          <t>稀有宝箱22</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>160</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tradable, Stackable</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #24</t>
+          <t>串行List行，归属 reward_holder_003 #22</t>
         </is>
       </c>
     </row>
@@ -1866,37 +1866,37 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>reward_025</t>
+          <t>reward_023</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>体力补给25</t>
+          <t>经验药水23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TestOnly</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #25</t>
+          <t>串行List行，归属 reward_holder_003 #23</t>
         </is>
       </c>
     </row>
@@ -1923,37 +1923,37 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>reward_026</t>
+          <t>reward_024</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>钥匙碎片26</t>
+          <t>强化石24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Tradable, Stackable</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #26</t>
+          <t>串行List行，归属 reward_holder_003 #24</t>
         </is>
       </c>
     </row>
@@ -1980,37 +1980,37 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>reward_027</t>
+          <t>reward_025</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>活动代币27</t>
+          <t>体力补给25</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>175</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>TestOnly</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #27</t>
+          <t>串行List行，归属 reward_holder_003 #25</t>
         </is>
       </c>
     </row>
@@ -2037,37 +2037,37 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>reward_028</t>
+          <t>reward_026</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>装备图纸28</t>
+          <t>钥匙碎片26</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #28</t>
+          <t>串行List行，归属 reward_holder_003 #26</t>
         </is>
       </c>
     </row>
@@ -2094,37 +2094,37 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>reward_029</t>
+          <t>reward_027</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>技能书29</t>
+          <t>活动代币27</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Tradable, Stackable</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #29</t>
+          <t>串行List行，归属 reward_holder_003 #27</t>
         </is>
       </c>
     </row>
@@ -2151,37 +2151,37 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>reward_030</t>
+          <t>reward_028</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>宝石礼包30</t>
+          <t>装备图纸28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>190</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TestOnly</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_003 #30</t>
+          <t>串行List行，归属 reward_holder_003 #28</t>
         </is>
       </c>
     </row>
@@ -2193,12 +2193,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>reward_holder_004</t>
+          <t>reward_holder_003</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>第4组奖励</t>
+          <t>第3组奖励</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2208,37 +2208,37 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>reward_001</t>
+          <t>reward_029</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>通关金币</t>
+          <t>技能书29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>114514</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Tradable, Stackable</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>嵌套字段测试</t>
+          <t>串行List行，归属 reward_holder_003 #29</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>reward_holder_004</t>
+          <t>reward_holder_003</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>第4组奖励</t>
+          <t>第3组奖励</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>reward_002</t>
+          <t>reward_030</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>稀有宝箱</t>
+          <t>宝石礼包30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2280,22 +2280,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>TestOnly</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>嵌套字段测试</t>
+          <t>串行List行，归属 reward_holder_003 #30</t>
         </is>
       </c>
     </row>
@@ -2322,22 +2322,22 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>reward_031</t>
+          <t>reward_001</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>通关金币31</t>
+          <t>通关金币</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>114514</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #31</t>
+          <t>嵌套字段测试</t>
         </is>
       </c>
     </row>
@@ -2379,17 +2379,17 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>reward_032</t>
+          <t>reward_002</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>稀有宝箱3288888888</t>
+          <t>稀有宝箱</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2399,17 +2399,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #32</t>
+          <t>嵌套字段测试</t>
         </is>
       </c>
     </row>
@@ -2436,37 +2436,37 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>reward_033</t>
+          <t>reward_031</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>经验药水33</t>
+          <t>通关金币31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>205</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #33</t>
+          <t>串行List行，归属 reward_holder_004 #31</t>
         </is>
       </c>
     </row>
@@ -2493,37 +2493,37 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>reward_034</t>
+          <t>reward_032</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>强化石34</t>
+          <t>稀有宝箱3288888888</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Tradable, Stackable</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #34</t>
+          <t>串行List行，归属 reward_holder_004 #32</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>reward_035</t>
+          <t>reward_033</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>体力补给35</t>
+          <t>经验药水33</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2565,22 +2565,22 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TestOnly</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #35</t>
+          <t>串行List行，归属 reward_holder_004 #33</t>
         </is>
       </c>
     </row>
@@ -2607,37 +2607,37 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>reward_036</t>
+          <t>reward_034</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>钥匙碎片36</t>
+          <t>强化石34</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Tradable, Stackable</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #36</t>
+          <t>串行List行，归属 reward_holder_004 #34</t>
         </is>
       </c>
     </row>
@@ -2664,37 +2664,37 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>reward_037</t>
+          <t>reward_035</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>活动代币37</t>
+          <t>体力补给35</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Stackable</t>
+          <t>TestOnly</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #37</t>
+          <t>串行List行，归属 reward_holder_004 #35</t>
         </is>
       </c>
     </row>
@@ -2721,37 +2721,37 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>reward_038</t>
+          <t>reward_036</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>装备图纸38</t>
+          <t>钥匙碎片36</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>None</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #38</t>
+          <t>串行List行，归属 reward_holder_004 #36</t>
         </is>
       </c>
     </row>
@@ -2778,37 +2778,37 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>reward_039</t>
+          <t>reward_037</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>技能书39</t>
+          <t>活动代币37</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Tradable, Stackable</t>
+          <t>Stackable</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #39</t>
+          <t>串行List行，归属 reward_holder_004 #37</t>
         </is>
       </c>
     </row>
@@ -2835,37 +2835,37 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>reward_040</t>
+          <t>reward_038</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>宝石礼包40</t>
+          <t>装备图纸38</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Normal</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TestOnly</t>
+          <t>Tradable</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_004 #40</t>
+          <t>串行List行，归属 reward_holder_004 #38</t>
         </is>
       </c>
     </row>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>reward_holder_005</t>
+          <t>reward_holder_004</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>第5组奖励</t>
+          <t>第4组奖励</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2892,17 +2892,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>reward_001</t>
+          <t>reward_039</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>通关金币</t>
+          <t>技能书39</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2912,17 +2912,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Tradable, Stackable</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>9999</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>嵌套字段测试</t>
+          <t>串行List行，归属 reward_holder_004 #39</t>
         </is>
       </c>
     </row>
@@ -2934,12 +2934,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>reward_holder_005</t>
+          <t>reward_holder_004</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>第5组奖励</t>
+          <t>第4组奖励</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2949,37 +2949,37 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>reward_002</t>
+          <t>reward_040</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>稀有宝箱</t>
+          <t>宝石礼包40</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>250</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Normal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tradable</t>
+          <t>TestOnly</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>嵌套字段测试</t>
+          <t>串行List行，归属 reward_holder_004 #40</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>reward_041</t>
+          <t>reward_001</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>通关金币41</t>
+          <t>通关金币</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>串行List行，归属 reward_holder_005 #41</t>
+          <t>嵌套字段测试</t>
         </is>
       </c>
     </row>
@@ -3063,49 +3063,166 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
+          <t>reward_002</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>稀有宝箱</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Tradable</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>嵌套字段测试</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>reward_holder_005</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>第5组奖励</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>reward_041</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>通关金币41</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>3.05</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>串行List行，归属 reward_holder_005 #41</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>reward_holder_005</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>第5组奖励</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>reward_042</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>稀有宝箱42</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Epic</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Stackable</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>串行List行，归属 reward_holder_005 #42</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A5:A1048576">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="A7:A1048576">
       <formula1>"skip,ignore,required,patch,replace,owner,delete,debug,debug:patch,debug:delete,comment:"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H5:H1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B5:K5">
+      <formula1>"required,unique,required;unique,json,asset,range:1..99,regex:^[a-z0-9_]+$"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H7:H1048576">
       <formula1>"Normal,Rare,Epic"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I5:I1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I7:I1048576">
       <formula1>"None,Tradable,Stackable,TestOnly"</formula1>
     </dataValidation>
   </dataValidations>
